--- a/Roguelike/Assets/Prefabs/Enemy/Enemy.xlsx
+++ b/Roguelike/Assets/Prefabs/Enemy/Enemy.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hosokawashigeki/Documents/Unity/Roguelike/Assets/Prefabs/Enemy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39DE6DF4-5066-A64F-9179-DB7FA46B6984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82173A15-1045-B141-B281-7B1557C65920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28800" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{0B4B62AB-7895-A649-A0C3-92C764A8A94D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -509,7 +509,7 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="2:7">
@@ -529,7 +529,7 @@
         <v>4</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:7">
@@ -549,7 +549,7 @@
         <v>4</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="2:7">
@@ -569,7 +569,7 @@
         <v>2</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="2:7">
@@ -589,7 +589,7 @@
         <v>3</v>
       </c>
       <c r="G8">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="2:7">
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="2:7">
@@ -626,10 +626,10 @@
         <v>17</v>
       </c>
       <c r="F10">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="2:7">
@@ -646,10 +646,10 @@
         <v>19</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G11">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="2:7">
@@ -660,7 +660,7 @@
         <v>12</v>
       </c>
       <c r="D12">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E12">
         <v>25</v>
@@ -669,7 +669,7 @@
         <v>25</v>
       </c>
       <c r="G12">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="2:7">
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
       <c r="G13">
-        <v>31</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
